--- a/Datos_Restaurante.xlsx
+++ b/Datos_Restaurante.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ntact\Downloads\Plantilla_Restaurante\Plantilla_Restaurante\Plantilla_Restaurante\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11693032-BA9F-4703-9411-F0ED4D2EAB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECCF6283-0290-4C1B-8EAF-2CF179E7FD12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1244,10 +1244,10 @@
     <t>Puedes poner aquí una descripcion particular de tu negocio, lo que sea que quieras poner</t>
   </si>
   <si>
-    <t>© Tacos Don Pepe. Todos los derechos reservados.</t>
-  </si>
-  <si>
-    <t>No</t>
+    <t>© Restaurante Mariscos. Todos los derechos reservados.</t>
+  </si>
+  <si>
+    <t>Sí</t>
   </si>
 </sst>
 </file>
@@ -3123,7 +3123,7 @@
         <v>127</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>282</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>128</v>
@@ -3134,7 +3134,7 @@
         <v>129</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>130</v>
